--- a/reports/二级子公司D_现金流量表_2025-06.xlsx
+++ b/reports/二级子公司D_现金流量表_2025-06.xlsx
@@ -1957,16 +1957,8 @@
           <t>1</t>
         </is>
       </c>
-      <c r="F3" s="28" t="inlineStr">
-        <is>
-          <t>－</t>
-        </is>
-      </c>
-      <c r="G3" s="28" t="inlineStr">
-        <is>
-          <t>－</t>
-        </is>
-      </c>
+      <c r="F3" s="28" t="n"/>
+      <c r="G3" s="28" t="n"/>
       <c r="I3" s="5" t="n"/>
     </row>
     <row r="4" ht="18" customHeight="1">
@@ -1996,10 +1988,10 @@
         </is>
       </c>
       <c r="F4" s="15" t="n">
-        <v>72306000</v>
+        <v>72667443</v>
       </c>
       <c r="G4" s="15" t="n">
-        <v>408564000</v>
+        <v>408495175</v>
       </c>
       <c r="I4" s="5" t="n"/>
     </row>
@@ -2030,10 +2022,10 @@
         </is>
       </c>
       <c r="F5" s="15" t="n">
-        <v>0</v>
+        <v>1471305</v>
       </c>
       <c r="G5" s="15" t="n">
-        <v>0</v>
+        <v>8353080</v>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
@@ -2063,10 +2055,10 @@
         </is>
       </c>
       <c r="F6" s="15" t="n">
-        <v>0</v>
+        <v>742021</v>
       </c>
       <c r="G6" s="15" t="n">
-        <v>0</v>
+        <v>4176931</v>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
@@ -2096,10 +2088,10 @@
         </is>
       </c>
       <c r="F7" s="15" t="n">
-        <v>0</v>
+        <v>368560</v>
       </c>
       <c r="G7" s="15" t="n">
-        <v>0</v>
+        <v>2087690</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
@@ -2129,10 +2121,10 @@
         </is>
       </c>
       <c r="F8" s="15" t="n">
-        <v>0</v>
+        <v>296017</v>
       </c>
       <c r="G8" s="15" t="n">
-        <v>0</v>
+        <v>1671172</v>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
@@ -2162,10 +2154,10 @@
         </is>
       </c>
       <c r="F9" s="15" t="n">
-        <v>0</v>
+        <v>221822</v>
       </c>
       <c r="G9" s="15" t="n">
-        <v>0</v>
+        <v>1252394</v>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
@@ -2195,10 +2187,10 @@
         </is>
       </c>
       <c r="F10" s="15" t="n">
-        <v>0</v>
+        <v>147538</v>
       </c>
       <c r="G10" s="15" t="n">
-        <v>0</v>
+        <v>835664</v>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
@@ -2228,10 +2220,10 @@
         </is>
       </c>
       <c r="F11" s="15" t="n">
-        <v>0</v>
+        <v>111237</v>
       </c>
       <c r="G11" s="15" t="n">
-        <v>0</v>
+        <v>626197</v>
       </c>
     </row>
     <row r="12" ht="18" customHeight="1">
@@ -2261,10 +2253,10 @@
         </is>
       </c>
       <c r="F12" s="15" t="n">
-        <v>0</v>
+        <v>73592</v>
       </c>
       <c r="G12" s="15" t="n">
-        <v>0</v>
+        <v>417793</v>
       </c>
     </row>
     <row r="13" ht="18" customHeight="1">
@@ -2294,10 +2286,10 @@
         </is>
       </c>
       <c r="F13" s="15" t="n">
-        <v>0</v>
+        <v>185688</v>
       </c>
       <c r="G13" s="15" t="n">
-        <v>0</v>
+        <v>1043841</v>
       </c>
     </row>
     <row r="14" ht="18" customHeight="1">
@@ -2327,10 +2319,10 @@
         </is>
       </c>
       <c r="F14" s="15" t="n">
-        <v>0</v>
+        <v>92404</v>
       </c>
       <c r="G14" s="15" t="n">
-        <v>0</v>
+        <v>524795</v>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1">
@@ -2360,10 +2352,10 @@
         </is>
       </c>
       <c r="F15" s="15" t="n">
-        <v>0</v>
+        <v>59015</v>
       </c>
       <c r="G15" s="15" t="n">
-        <v>0</v>
+        <v>331979</v>
       </c>
     </row>
     <row r="16" ht="18" customHeight="1">
@@ -2393,10 +2385,10 @@
         </is>
       </c>
       <c r="F16" s="15" t="n">
-        <v>185400</v>
+        <v>184739</v>
       </c>
       <c r="G16" s="15" t="n">
-        <v>1047600</v>
+        <v>1047427</v>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
@@ -2426,10 +2418,10 @@
         </is>
       </c>
       <c r="F17" s="15" t="n">
-        <v>1236000</v>
+        <v>1238790</v>
       </c>
       <c r="G17" s="15" t="n">
-        <v>6984000</v>
+        <v>6986028</v>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
@@ -2546,7 +2538,7 @@
         </is>
       </c>
       <c r="F21" s="20" t="n">
-        <v>73727400</v>
+        <v>77860171</v>
       </c>
       <c r="G21" s="20" t="n"/>
     </row>
@@ -2577,10 +2569,10 @@
         </is>
       </c>
       <c r="F22" s="15" t="n">
-        <v>47380000</v>
+        <v>47596769</v>
       </c>
       <c r="G22" s="15" t="n">
-        <v>267720000</v>
+        <v>267631657</v>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
@@ -2610,10 +2602,10 @@
         </is>
       </c>
       <c r="F23" s="15" t="n">
-        <v>0</v>
+        <v>490298</v>
       </c>
       <c r="G23" s="15" t="n">
-        <v>0</v>
+        <v>2784885</v>
       </c>
     </row>
     <row r="24" ht="18" customHeight="1">
@@ -2643,10 +2635,10 @@
         </is>
       </c>
       <c r="F24" s="15" t="n">
-        <v>0</v>
+        <v>371361</v>
       </c>
       <c r="G24" s="15" t="n">
-        <v>0</v>
+        <v>2088056</v>
       </c>
     </row>
     <row r="25" ht="18" customHeight="1">
@@ -2676,10 +2668,10 @@
         </is>
       </c>
       <c r="F25" s="15" t="n">
-        <v>0</v>
+        <v>245332</v>
       </c>
       <c r="G25" s="15" t="n">
-        <v>0</v>
+        <v>1392046</v>
       </c>
     </row>
     <row r="26" ht="18" customHeight="1">
@@ -2709,10 +2701,10 @@
         </is>
       </c>
       <c r="F26" s="15" t="n">
-        <v>0</v>
+        <v>185368</v>
       </c>
       <c r="G26" s="15" t="n">
-        <v>0</v>
+        <v>1044325</v>
       </c>
     </row>
     <row r="27" ht="18" customHeight="1">
@@ -2742,10 +2734,10 @@
         </is>
       </c>
       <c r="F27" s="15" t="n">
-        <v>0</v>
+        <v>122970</v>
       </c>
       <c r="G27" s="15" t="n">
-        <v>0</v>
+        <v>695846</v>
       </c>
     </row>
     <row r="28" ht="18" customHeight="1">
@@ -2775,10 +2767,10 @@
         </is>
       </c>
       <c r="F28" s="15" t="n">
-        <v>0</v>
+        <v>92882</v>
       </c>
       <c r="G28" s="15" t="n">
-        <v>0</v>
+        <v>524945</v>
       </c>
     </row>
     <row r="29" ht="18" customHeight="1">
@@ -2808,10 +2800,10 @@
         </is>
       </c>
       <c r="F29" s="15" t="n">
-        <v>7416000</v>
+        <v>7426511</v>
       </c>
       <c r="G29" s="15" t="n">
-        <v>41904000</v>
+        <v>41885208</v>
       </c>
     </row>
     <row r="30" ht="18" customHeight="1">
@@ -2841,10 +2833,10 @@
         </is>
       </c>
       <c r="F30" s="15" t="n">
-        <v>3914000</v>
+        <v>3902754</v>
       </c>
       <c r="G30" s="15" t="n">
-        <v>22116000</v>
+        <v>22125772</v>
       </c>
     </row>
     <row r="31" ht="18" customHeight="1">
@@ -2874,10 +2866,10 @@
         </is>
       </c>
       <c r="F31" s="15" t="n">
-        <v>1545000</v>
+        <v>1551225</v>
       </c>
       <c r="G31" s="15" t="n">
-        <v>8730000</v>
+        <v>8726605</v>
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
@@ -2936,7 +2928,7 @@
         </is>
       </c>
       <c r="F33" s="20" t="n">
-        <v>60255000</v>
+        <v>61985470</v>
       </c>
       <c r="G33" s="20" t="n"/>
     </row>
@@ -2967,7 +2959,7 @@
         </is>
       </c>
       <c r="F34" s="20" t="n">
-        <v>13472400</v>
+        <v>15874701</v>
       </c>
       <c r="G34" s="20" t="n"/>
     </row>
@@ -3093,10 +3085,10 @@
         </is>
       </c>
       <c r="F38" s="15" t="n">
-        <v>80000</v>
+        <v>80028</v>
       </c>
       <c r="G38" s="15" t="n">
-        <v>480000</v>
+        <v>479889</v>
       </c>
     </row>
     <row r="39" ht="18" customHeight="1">
@@ -3159,10 +3151,10 @@
         </is>
       </c>
       <c r="F40" s="15" t="n">
-        <v>700000</v>
+        <v>702304</v>
       </c>
       <c r="G40" s="15" t="n">
-        <v>4200000</v>
+        <v>4198605</v>
       </c>
     </row>
     <row r="41" ht="18" customHeight="1">
@@ -3192,10 +3184,10 @@
         </is>
       </c>
       <c r="F41" s="15" t="n">
-        <v>420000</v>
+        <v>418186</v>
       </c>
       <c r="G41" s="15" t="n">
-        <v>2520000</v>
+        <v>2520840</v>
       </c>
     </row>
     <row r="42" ht="18" customHeight="1">
@@ -3225,7 +3217,7 @@
         </is>
       </c>
       <c r="F42" s="20" t="n">
-        <v>780000</v>
+        <v>782332</v>
       </c>
       <c r="G42" s="20" t="n"/>
     </row>
@@ -3256,10 +3248,10 @@
         </is>
       </c>
       <c r="F43" s="15" t="n">
-        <v>8000000</v>
+        <v>7960297</v>
       </c>
       <c r="G43" s="15" t="n">
-        <v>48000000</v>
+        <v>48011204</v>
       </c>
     </row>
     <row r="44" ht="18" customHeight="1">
@@ -3289,10 +3281,10 @@
         </is>
       </c>
       <c r="F44" s="15" t="n">
-        <v>1200000</v>
+        <v>1205411</v>
       </c>
       <c r="G44" s="15" t="n">
-        <v>7200000</v>
+        <v>7198965</v>
       </c>
     </row>
     <row r="45" ht="18" customHeight="1">
@@ -3322,10 +3314,10 @@
         </is>
       </c>
       <c r="F45" s="15" t="n">
-        <v>5500000</v>
+        <v>5480286</v>
       </c>
       <c r="G45" s="15" t="n">
-        <v>33000000</v>
+        <v>33001285</v>
       </c>
     </row>
     <row r="46" ht="18" customHeight="1">
@@ -3454,10 +3446,10 @@
         </is>
       </c>
       <c r="F49" s="15" t="n">
-        <v>180000</v>
+        <v>180431</v>
       </c>
       <c r="G49" s="15" t="n">
-        <v>1080000</v>
+        <v>1079664</v>
       </c>
     </row>
     <row r="50" ht="18" customHeight="1">
@@ -3487,7 +3479,7 @@
         </is>
       </c>
       <c r="F50" s="20" t="n">
-        <v>8180000</v>
+        <v>8140728</v>
       </c>
       <c r="G50" s="20" t="n"/>
     </row>
@@ -3518,7 +3510,7 @@
         </is>
       </c>
       <c r="F51" s="20" t="n">
-        <v>-7400000</v>
+        <v>-7358396</v>
       </c>
       <c r="G51" s="20" t="n"/>
     </row>
@@ -3578,10 +3570,10 @@
         </is>
       </c>
       <c r="F53" s="15" t="n">
-        <v>1500000</v>
+        <v>1507306</v>
       </c>
       <c r="G53" s="15" t="n">
-        <v>9000000</v>
+        <v>8998144</v>
       </c>
     </row>
     <row r="54" ht="18" customHeight="1">
@@ -3644,10 +3636,10 @@
         </is>
       </c>
       <c r="F55" s="15" t="n">
-        <v>2500000</v>
+        <v>2507987</v>
       </c>
       <c r="G55" s="15" t="n">
-        <v>15000000</v>
+        <v>14999951</v>
       </c>
     </row>
     <row r="56" ht="18" customHeight="1">
@@ -3677,10 +3669,10 @@
         </is>
       </c>
       <c r="F56" s="15" t="n">
-        <v>2500000</v>
+        <v>2495499</v>
       </c>
       <c r="G56" s="15" t="n">
-        <v>15000000</v>
+        <v>14998433</v>
       </c>
     </row>
     <row r="57" ht="18" customHeight="1">
@@ -3710,10 +3702,10 @@
         </is>
       </c>
       <c r="F57" s="15" t="n">
-        <v>80000</v>
+        <v>80017</v>
       </c>
       <c r="G57" s="15" t="n">
-        <v>480000</v>
+        <v>480096</v>
       </c>
     </row>
     <row r="58" ht="18" customHeight="1">
@@ -3743,7 +3735,7 @@
         </is>
       </c>
       <c r="F58" s="20" t="n">
-        <v>4080000</v>
+        <v>4095310</v>
       </c>
       <c r="G58" s="20" t="n"/>
     </row>
@@ -3774,10 +3766,10 @@
         </is>
       </c>
       <c r="F59" s="15" t="n">
-        <v>2000000</v>
+        <v>1994304</v>
       </c>
       <c r="G59" s="15" t="n">
-        <v>12000000</v>
+        <v>12003884</v>
       </c>
     </row>
     <row r="60" ht="18" customHeight="1">
@@ -3807,10 +3799,10 @@
         </is>
       </c>
       <c r="F60" s="15" t="n">
-        <v>2000000</v>
+        <v>2008021</v>
       </c>
       <c r="G60" s="15" t="n">
-        <v>12000000</v>
+        <v>11995960</v>
       </c>
     </row>
     <row r="61" ht="18" customHeight="1">
@@ -3840,10 +3832,10 @@
         </is>
       </c>
       <c r="F61" s="15" t="n">
-        <v>320000</v>
+        <v>318479</v>
       </c>
       <c r="G61" s="15" t="n">
-        <v>1920000</v>
+        <v>1920605</v>
       </c>
     </row>
     <row r="62" ht="18" customHeight="1">
@@ -3902,10 +3894,10 @@
         </is>
       </c>
       <c r="F63" s="15" t="n">
-        <v>280000</v>
+        <v>278677</v>
       </c>
       <c r="G63" s="15" t="n">
-        <v>1680000</v>
+        <v>1680298</v>
       </c>
     </row>
     <row r="64" ht="18" customHeight="1">
@@ -3935,10 +3927,10 @@
         </is>
       </c>
       <c r="F64" s="15" t="n">
-        <v>40000</v>
+        <v>40158</v>
       </c>
       <c r="G64" s="15" t="n">
-        <v>240000</v>
+        <v>239982</v>
       </c>
     </row>
     <row r="65" ht="18" customHeight="1">
@@ -3968,7 +3960,7 @@
         </is>
       </c>
       <c r="F65" s="20" t="n">
-        <v>2360000</v>
+        <v>2352941</v>
       </c>
       <c r="G65" s="20" t="n"/>
     </row>
@@ -3999,7 +3991,7 @@
         </is>
       </c>
       <c r="F66" s="20" t="n">
-        <v>1720000</v>
+        <v>1742369</v>
       </c>
       <c r="G66" s="20" t="n"/>
     </row>
@@ -4059,7 +4051,7 @@
         </is>
       </c>
       <c r="F68" s="20" t="n">
-        <v>7792400</v>
+        <v>10258674</v>
       </c>
       <c r="G68" s="20" t="n"/>
     </row>
@@ -4090,7 +4082,9 @@
         </is>
       </c>
       <c r="F69" s="23" t="n"/>
-      <c r="G69" s="20" t="n"/>
+      <c r="G69" s="20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="70" ht="18" customHeight="1">
       <c r="A70" s="9" t="inlineStr">
@@ -4119,7 +4113,7 @@
         </is>
       </c>
       <c r="F70" s="26" t="n">
-        <v>7792400</v>
+        <v>10258674</v>
       </c>
       <c r="G70" s="26" t="n"/>
     </row>
